--- a/docs/package/05_Delivery/Upload_Templates/Insurance_Company_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Insurance_Company_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
   <si>
     <t xml:space="preserve">Insurance Company Code</t>
   </si>
@@ -39,10 +39,10 @@
     <t xml:space="preserve">Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State</t>
+    <t xml:space="preserve">City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
   </si>
   <si>
     <t xml:space="preserve">Country</t>
@@ -69,6 +69,15 @@
     <t xml:space="preserve">Default Billing Mode</t>
   </si>
   <si>
+    <t xml:space="preserve">IC Certificate of Authority No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificate of Authority Valid Until</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC Licence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -90,7 +99,7 @@
     <t xml:space="preserve">Skyland Plaza, Sen. Gil Puyat Ave.</t>
   </si>
   <si>
-    <t xml:space="preserve">Makati</t>
+    <t xml:space="preserve">Makati City</t>
   </si>
   <si>
     <t xml:space="preserve">Metro Manila</t>
@@ -219,6 +228,21 @@
     <t xml:space="preserve">defaultBillingMode</t>
   </si>
   <si>
+    <t xml:space="preserve">icCertificateNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icCertificateValidUntil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-life, Life, Composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icLineOfBusiness</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active when empty</t>
   </si>
   <si>
@@ -267,7 +291,7 @@
     <t xml:space="preserve">Required columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurance Company Code, Insurance Company Name, City, State, Country, Email ID, Phone Number (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
+    <t xml:space="preserve">Insurance Company Code, Insurance Company Name, City / Municipality, Province, Country, Email ID, Phone Number (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Header row</t>
@@ -432,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -443,7 +467,7 @@
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
@@ -453,10 +477,13 @@
     <col min="16" max="16" width="37" customWidth="1"/>
     <col min="17" max="17" width="42" customWidth="1"/>
     <col min="18" max="18" width="26" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="19" max="19" width="37" customWidth="1"/>
+    <col min="20" max="20" width="42" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20" customHeight="1">
+    <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -514,55 +541,64 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -572,7 +608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -585,22 +621,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -608,16 +644,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -625,16 +661,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -642,16 +678,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -659,16 +695,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -676,16 +712,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -693,16 +729,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -710,13 +746,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -724,13 +760,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -738,16 +774,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -755,16 +791,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -772,16 +808,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -789,16 +825,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -806,16 +842,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -823,16 +859,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -840,16 +876,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -857,16 +893,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -874,16 +910,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
@@ -891,19 +927,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -911,16 +947,61 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>70</v>
+      <c r="D22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -939,106 +1020,106 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Insurance_Company_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Insurance_Company_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="103">
   <si>
     <t xml:space="preserve">Insurance Company Code</t>
   </si>
@@ -270,12 +270,6 @@
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Insurance Company &gt; Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/insurance-company/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -324,10 +318,10 @@
     <t xml:space="preserve">Each row creates a new record, checked exactly like Add on the screen. A row whose code already exists is refused (edit existing records on the screen).</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -335,9 +329,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -364,8 +358,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,6 +421,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,9 +470,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -447,6 +493,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1114,14 +1167,6 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
